--- a/AtchisonRegime/Outputs/India/df_regInflation_India.xlsx
+++ b/AtchisonRegime/Outputs/India/df_regInflation_India.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H773"/>
+  <dimension ref="A1:H774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20527,24 +20527,50 @@
         <v>45747</v>
       </c>
       <c r="B773" t="n">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="C773" t="n">
-        <v>2.760000000000005</v>
+        <v>2.880000000000005</v>
       </c>
       <c r="D773" t="n">
-        <v>4.868611111111111</v>
+        <v>4.878611111111111</v>
       </c>
       <c r="E773" t="n">
-        <v>1.367174673295897</v>
+        <v>1.351255823886601</v>
       </c>
       <c r="F773" t="b">
         <v>0</v>
       </c>
       <c r="G773" t="n">
-        <v>-1.542312882396952</v>
+        <v>-1.479076778638796</v>
       </c>
       <c r="H773" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B774" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C774" t="n">
+        <v>2.830000000000005</v>
+      </c>
+      <c r="D774" t="n">
+        <v>4.784722222222222</v>
+      </c>
+      <c r="E774" t="n">
+        <v>1.364885104763953</v>
+      </c>
+      <c r="F774" t="b">
+        <v>0</v>
+      </c>
+      <c r="G774" t="n">
+        <v>-1.432151479563748</v>
+      </c>
+      <c r="H774" t="b">
         <v>0</v>
       </c>
     </row>
